--- a/pensum/ol16/OL16_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol16/OL16_Klasseoppgaver_v5.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="163">
   <si>
     <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 16: Grupper, kommunikasjon og konflikt (V5)</t>
   </si>
@@ -143,9 +143,18 @@
     <t xml:space="preserve">a)  Hvor mange prosent av de 105 servicebesøkene i vårhalvåret måtte gjøres på nytt? Én desimal.</t>
   </si>
   <si>
+    <t xml:space="preserve">Formel og begrep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andel = del / helhet × 100. Ledelsen har ansvaret for at relevant informasjon når dem som trenger den, når de trenger den (Organisasjon og ledelse 16.4).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hvor mange kroner i tapt fakturering kostet de nye besøkene i vårhalvåret? Antall besøk × timer × timepris.</t>
   </si>
   <si>
+    <t xml:space="preserve">Tapt fakturering = antall besøk × timer × timepris.</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Hvor i kommunikasjonsmodellen sviktet det mest, hvis vi bruker lærebokas beskrivelse av modellen og kommunikasjonsformene?   A: Fysisk støy: montøren leste meldingen i bilen   B: Kodingen og mediet: Tom koder kort, og en SMS er enveis og indirekte, så ingenting kan oppklares   C: Mottakeren: montørene har antipatier mot Tom   (skriv bokstaven)</t>
   </si>
   <si>
@@ -170,6 +179,24 @@
     <t xml:space="preserve">e)  Tom sier: «De leser ikke meldingene ordentlig.» Vurder forklaringen hans med kommunikasjonsmodellen og årsakene til brudd, og foreslå tiltak med navn, handling og frist. Bruk minst ett tall. Tre–fire setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Kommunikasjonsmodellen (16.2), årsaker til brudd hos avsender og mottaker (16.3) og tiltak (Organisasjon og ledelse 16.4).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hint, hvis du står fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tallene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andel: 9 / 105 × 100. Tapt fakturering: 9 besøk × 3 timer × 890 kr. Spør deg så: hvilket ledd i modellen er nytt hver gang?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modellen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom koder, SMS-en er mediet, montøren dekoder. Kan montøren spørre om noe kvelden før? Boka skiller mellom enveis og toveis, direkte og indirekte.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 16, avsnitt 16.2 (kommunikasjonsmodellen, direkte og indirekte, enveis og toveis), 16.3 (årsaker hos avsender og mottaker) og 16.4 (tiltak). Servicebesøkene: MA04 og faktaarket. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -263,12 +290,30 @@
     <t xml:space="preserve">c)  Hvor mange kroner i fakturerbar tid koster mandagsmøtet i året? Personer × timer × uker × timepris.</t>
   </si>
   <si>
+    <t xml:space="preserve">Møtekostnad = personer × timer × uker × timepris. Regelmessige møter krever at de er godt forberedt (Organisasjon og ledelse 16.4).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  En student sier: «Praten over kaffen og i bilen er bare sladder. Mona bør gi alle beskjeder skriftlig.» Hva sier boka?   A: Studenten har rett: formell kommunikasjon er alltid bedre   B: Uformelle kanaler kan brukes bevisst til å forberede, presisere og utdype; alt til sin tid   C: Uformell kommunikasjon hører ikke hjemme på jobb   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Den ene montøren sier: «Mona spør aldri hvordan det går med oss.» Hva sier det om kommunikasjonen i Fjell, og hva bør Mona gjøre? Bruk tallet fra c og minst to tiltak fra læreboka. Tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Verbal og nonverbal kommunikasjon og dobbeltkommunikasjon (16.2.1), og tiltakene regelmessige møter, aktiv lytting, uformelle kanaler og medarbeidersamtaler (Organisasjon og ledelse 16.4).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gruppene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formell: målrettet, roller, kvalifikasjoner. Uformell: felles interesse. Primærgruppe: familien. Referansegruppe: den du sammenlikner deg med.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ord og kropp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hva sier Mona med ord, og hva sier hun med mobilen og ved å reise seg? Møtet: 3 × 0,5 × 46 × 890. For d: les tiltaket om uformelle kanaler i 16.4.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 16, avsnitt 16.1 (formelle og uformelle grupper, primær- og referansegrupper), 16.2 (verbal og nonverbal, dobbeltkommunikasjon, formell og uformell kommunikasjon) og 16.4 (uformelle kanaler, regelmessige møter, medarbeidersamtaler). Fjell Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -344,6 +389,21 @@
     <t xml:space="preserve">e)  Legg en rekkefølge for Kari: hvilken sak tar hun først, og hvorfor? Bruk konfliktens intensitetsnivåer og strategiene. Tre–fire setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Konfliktens intensitetsnivåer (16.5), konflikttypene (16.6) og konflikthåndteringsstrategiene (Organisasjon og ledelse 16.7).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Typen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Er de enige om målet? Da er det virkemiddel. Er de uenige om hva som skal gå først? Mål. Er det én ting bare én kan få? Interesse.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strategien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samarbeid når partene har noe å lære av hverandre. Konfrontasjon når saken er viktig og må avgjøres raskt. For e: hvilken sak har et «alltid» i seg?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 16, avsnitt 16.5 (konfliktens intensitetsnivåer), 16.6 (fire konflikttyper) og 16.7 (fem konflikthåndteringsstrategier, figur 16.3). Sakene er fra v4, sammendraget og appen til kap. 16. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -428,10 +488,28 @@
     <t xml:space="preserve">c)  Hvor mange kroner i året koster lønnstillegget på 10 % for Fjell, med 46,8 % sosiale kostnader?</t>
   </si>
   <si>
+    <t xml:space="preserve">Lønnskostnad = lønn × (1 + sats for sosiale kostnader); 46,8 % er Fjells sats (Økonomistyring tabell 2.4, ikke i kap. 16).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Hvilken konflikthåndteringsstrategi passer best for Mona, etter bokas beskrivelse av når strategiene er naturlige?   A: Konfrontasjon: Mona eier bedriften og bestemmer lønna   B: Kompromiss: partene er noenlunde jevnbyrdige, og begge kan gi avkall på noe   C: Unnvikelse: la saken ligge til neste år   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Hva bør Mona gjøre med lønnskravet, og hvordan bør hun håndtere den andre montøren? Bruk tallene fra c og bokas begreper. Tre–fire setninger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Makt og avhengighet (16.5), interessekonflikt (16.6) og kompromiss (Organisasjon og ledelse 16.7). Lønnskostnad med 46,8 % sosiale kostnader.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Makten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tre regler: A kontrollerer et gode B ønsker; jo mer B ønsker det; jo vanskeligere B kan få det andre steder. Motmakt bygges med allianser eller kompetanse.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regningen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">560 000 × 0,10 × 1,468. Sammenlikn med driftsresultatet 144 240 kr. Og hva skjer hvis begge får det samme?</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 16, avsnitt 16.5 (makt- og avhengighetsrelasjoner, motmakt), 16.6 (interessekonflikter) og 16.7 (kompromiss). Lønn, sosiale kostnader og driftsresultat: Fjell-faktaarket. Fjell Elektro AS er en konstruert casebedrift.</t>
@@ -445,7 +523,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.##;\−#,##0.##;\0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -512,8 +590,30 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF2F4A6D"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -529,13 +629,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4F6FA"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFEEF2F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF2F8"/>
+        <bgColor rgb="FFF4F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8954A"/>
+        <bgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBF6EA"/>
+        <bgColor rgb="FFF4F6FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -588,7 +706,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -661,11 +779,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -702,8 +840,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF4F6FA"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFBF6EA"/>
+      <rgbColor rgb="FFEEF2F8"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -717,7 +855,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFF4F6FA"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -731,7 +869,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF5E6670"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFB8954A"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -1034,7 +1172,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1175,35 +1313,20 @@
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="17" t="str">
-        <f aca="false">IF(F19="","",IF(ABS(F19-(24030))&lt;=1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
+      <c r="B19" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="17" t="str">
-        <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+    </row>
+    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
         <v>41</v>
       </c>
@@ -1211,154 +1334,251 @@
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
+      <c r="F21" s="15"/>
+      <c r="G21" s="17" t="str">
+        <f aca="false">IF(F21="","",IF(ABS(F21-(24030))&lt;=1,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="17" t="str">
-        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+    </row>
+    <row r="24" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
         <v>43</v>
-      </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="17" t="str">
-        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>44</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="18"/>
+      <c r="F24" s="20"/>
       <c r="G24" s="17" t="str">
-        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="17" t="str">
-        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-      <c r="F26" s="18"/>
+      <c r="F26" s="20"/>
       <c r="G26" s="17" t="str">
-        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-    </row>
-    <row r="32" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
+      <c r="F27" s="20"/>
+      <c r="G27" s="17" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="17" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="17" t="str">
+        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="17" t="str">
+        <f aca="false">IF(F30="","",IF(UPPER(TRIM(F30))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="21"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="21"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+    </row>
+    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" s="22"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+    </row>
+    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B39" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="24"/>
+    </row>
+    <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B40" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
+    </row>
+    <row r="42" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="23">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B19:G19"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="B22:G22"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A28:G30"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:G34"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A43:G43"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1375,7 +1595,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1386,7 +1606,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1396,7 +1616,7 @@
     </row>
     <row r="4" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1407,7 +1627,7 @@
     </row>
     <row r="5" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1418,10 +1638,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -1430,11 +1650,11 @@
       <c r="G7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="s">
-        <v>55</v>
+      <c r="A8" s="25" t="s">
+        <v>64</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1443,11 +1663,11 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
-        <v>57</v>
+      <c r="A9" s="25" t="s">
+        <v>66</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1456,11 +1676,11 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="s">
-        <v>59</v>
+      <c r="A10" s="25" t="s">
+        <v>68</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1469,11 +1689,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
-        <v>61</v>
+      <c r="A11" s="25" t="s">
+        <v>70</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1482,11 +1702,11 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
-        <v>63</v>
+      <c r="A12" s="25" t="s">
+        <v>72</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1495,11 +1715,11 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="s">
-        <v>65</v>
+      <c r="A13" s="25" t="s">
+        <v>74</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1508,11 +1728,11 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="20" t="s">
-        <v>67</v>
+      <c r="A14" s="25" t="s">
+        <v>76</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -1521,11 +1741,11 @@
       <c r="G14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="20" t="s">
-        <v>69</v>
+      <c r="A15" s="25" t="s">
+        <v>78</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -1550,7 +1770,7 @@
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1559,13 +1779,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="18"/>
+      <c r="F19" s="20"/>
       <c r="G19" s="17" t="str">
         <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1573,13 +1793,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="18"/>
+      <c r="F20" s="20"/>
       <c r="G20" s="17" t="str">
         <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1587,13 +1807,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="18"/>
+      <c r="F21" s="20"/>
       <c r="G21" s="17" t="str">
         <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1601,13 +1821,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="18"/>
+      <c r="F22" s="20"/>
       <c r="G22" s="17" t="str">
         <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1615,13 +1835,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="18"/>
+      <c r="F23" s="20"/>
       <c r="G23" s="17" t="str">
         <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1629,13 +1849,13 @@
     </row>
     <row r="24" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="18"/>
+      <c r="F24" s="20"/>
       <c r="G24" s="17" t="str">
         <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="B","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1643,7 +1863,7 @@
     </row>
     <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -1655,80 +1875,143 @@
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="17" t="str">
-        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
+    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+    </row>
+    <row r="28" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="17" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-    </row>
-    <row r="32" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="21"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B37" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B38" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24"/>
+    </row>
+    <row r="40" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="30">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1749,11 +2032,16 @@
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A28:G30"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A41:G41"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1770,7 +2058,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1781,7 +2069,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1791,7 +2079,7 @@
     </row>
     <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1802,7 +2090,7 @@
     </row>
     <row r="5" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1813,10 +2101,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -1825,11 +2113,11 @@
       <c r="G7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="s">
-        <v>85</v>
+      <c r="A8" s="25" t="s">
+        <v>100</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1838,11 +2126,11 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
-        <v>87</v>
+      <c r="A9" s="25" t="s">
+        <v>102</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1851,11 +2139,11 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="s">
-        <v>89</v>
+      <c r="A10" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1864,11 +2152,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
-        <v>91</v>
+      <c r="A11" s="25" t="s">
+        <v>106</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1877,11 +2165,11 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
-        <v>93</v>
+      <c r="A12" s="25" t="s">
+        <v>108</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1890,11 +2178,11 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="s">
-        <v>95</v>
+      <c r="A13" s="25" t="s">
+        <v>110</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1919,13 +2207,13 @@
     </row>
     <row r="16" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
-      <c r="F16" s="18"/>
+      <c r="F16" s="20"/>
       <c r="G16" s="17" t="str">
         <f aca="false">IF(F16="","",IF(UPPER(TRIM(F16))="B","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1933,13 +2221,13 @@
     </row>
     <row r="17" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
-      <c r="F17" s="18"/>
+      <c r="F17" s="20"/>
       <c r="G17" s="17" t="str">
         <f aca="false">IF(F17="","",IF(UPPER(TRIM(F17))="C","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1947,7 +2235,7 @@
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1956,13 +2244,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="18"/>
+      <c r="F19" s="20"/>
       <c r="G19" s="17" t="str">
         <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1970,13 +2258,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="18"/>
+      <c r="F20" s="20"/>
       <c r="G20" s="17" t="str">
         <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1984,13 +2272,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="18"/>
+      <c r="F21" s="20"/>
       <c r="G21" s="17" t="str">
         <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1998,13 +2286,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="18"/>
+      <c r="F22" s="20"/>
       <c r="G22" s="17" t="str">
         <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2012,13 +2300,13 @@
     </row>
     <row r="23" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="18"/>
+      <c r="F23" s="20"/>
       <c r="G23" s="17" t="str">
         <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="B","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2026,7 +2314,7 @@
     </row>
     <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -2034,56 +2322,106 @@
       <c r="E24" s="7"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
+      <c r="A25" s="21"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-    </row>
-    <row r="29" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+    </row>
+    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+    </row>
+    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="B33" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+    </row>
+    <row r="35" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="26">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -2104,8 +2442,12 @@
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:G27"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A36:G36"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2122,7 +2464,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -2133,7 +2475,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2143,7 +2485,7 @@
     </row>
     <row r="4" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -2154,7 +2496,7 @@
     </row>
     <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2165,10 +2507,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -2177,11 +2519,11 @@
       <c r="G7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="s">
-        <v>110</v>
+      <c r="A8" s="25" t="s">
+        <v>130</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -2190,11 +2532,11 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
-        <v>112</v>
+      <c r="A9" s="25" t="s">
+        <v>132</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -2203,11 +2545,11 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="s">
-        <v>114</v>
+      <c r="A10" s="25" t="s">
+        <v>134</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -2216,11 +2558,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
-        <v>116</v>
+      <c r="A11" s="25" t="s">
+        <v>136</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -2229,11 +2571,11 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
-        <v>118</v>
+      <c r="A12" s="25" t="s">
+        <v>138</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -2242,11 +2584,11 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="s">
-        <v>120</v>
+      <c r="A13" s="25" t="s">
+        <v>140</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -2255,11 +2597,11 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="20" t="s">
-        <v>122</v>
+      <c r="A14" s="25" t="s">
+        <v>142</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -2268,11 +2610,11 @@
       <c r="G14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="20" t="s">
-        <v>124</v>
+      <c r="A15" s="25" t="s">
+        <v>144</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -2297,13 +2639,13 @@
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
-      <c r="F18" s="18"/>
+      <c r="F18" s="20"/>
       <c r="G18" s="17" t="str">
         <f aca="false">IF(F18="","",IF(UPPER(TRIM(F18))="B","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2311,7 +2653,7 @@
     </row>
     <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -2320,13 +2662,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="18"/>
+      <c r="F20" s="20"/>
       <c r="G20" s="17" t="str">
         <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2334,13 +2676,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="18"/>
+      <c r="F21" s="20"/>
       <c r="G21" s="17" t="str">
         <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2348,13 +2690,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="18"/>
+      <c r="F22" s="20"/>
       <c r="G22" s="17" t="str">
         <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2362,13 +2704,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="18"/>
+      <c r="F23" s="20"/>
       <c r="G23" s="17" t="str">
         <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2376,13 +2718,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="18"/>
+      <c r="F24" s="20"/>
       <c r="G24" s="17" t="str">
         <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2390,7 +2732,7 @@
     </row>
     <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -2402,80 +2744,143 @@
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="17" t="str">
-        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
+    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+    </row>
+    <row r="28" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="17" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-    </row>
-    <row r="32" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="21"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="B37" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="B38" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24"/>
+    </row>
+    <row r="40" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="30">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -2496,11 +2901,16 @@
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A28:G30"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A41:G41"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/pensum/ol16/OL16_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol16/OL16_Klasseoppgaver_v5.xlsx
@@ -95,7 +95,7 @@
     <t xml:space="preserve">Kort oppsummert: Avsenderen koder et budskap som går via et medium til mottakeren, som dekoder det (16.2, figur 16.2). Budskapet må være presist, og budskap og medium må være tilpasset hverandre. Direkte kommunikasjon gir bedre muligheter til å utdype, oppklare tvetydigheter og rydde vekk misforståelser. Årsaker til brudd ligger hos avsenderen (egen fortolkning, vag og utydelig, vanskelig språk, dobbeltkommunikasjon) og hos mottakeren (selektiv, sympatier og antipatier, dårlig lytter) (16.3). Ledelsen har særlig ansvar for at relevant informasjon i tilstrekkelige mengder når dem som trenger den, når de trenger den (16.4).</t>
   </si>
   <si>
-    <t xml:space="preserve">Casen er lagt til 2026/2027. Servicemontørene i Nordlys kjører hjemmefra rett til første kunde. Kundene ringer Tom, og Tom sender oppdraget på SMS til montøren kvelden før, for eksempel «Jordfeil, Haugveien 12, kl. 8». I vårhalvåret hadde serviceavdelingen 105 besøk. 9 av dem måtte gjøres på nytt fordi det kunden hadde sagt til Tom, ikke nådde montøren: montøren hadde ikke med riktig del, kunden var ikke hjemme, eller sikringsskapet sto et annet sted enn montøren trodde. Hvert nytt besøk tok 3 montørtimer som ikke kunne faktureres. Timeprisen er 890 kr uten mva. Tom sier: «De leser ikke meldingene ordentlig.» Gå fram slik: regn andelen og hva det kostet, finn leddet i kommunikasjonsmodellen som sviktet, sorter tiltakene, og vurder til slutt Toms forklaring.</t>
+    <t xml:space="preserve">Casen er lagt til 2026/2027. Servicemontørene i Nordlys kjører hjemmefra rett til første kunde. Kundene ringer Tom, og Tom sender oppdraget på SMS til montøren kvelden før, for eksempel «Jordfeil, Haugveien 12, kl. 8». I vårhalvåret hadde serviceavdelingen 105 besøk. 9 av dem måtte gjøres på nytt fordi det kunden hadde sagt til Tom, ikke nådde montøren: montøren hadde ikke med riktig del, kunden var ikke hjemme, eller sikringsskapet sto et annet sted enn montøren trodde. Hvert nytt besøk tok 3 montørtimer som ikke kunne faktureres. Timeprisen er 890 kr uten merverdiavgift. Tom sier: «De leser ikke meldingene ordentlig.» Gå fram slik: regn andelen og hva det kostet, finn leddet i kommunikasjonsmodellen som sviktet, sorter tiltakene, og vurder til slutt Toms forklaring.</t>
   </si>
   <si>
     <t xml:space="preserve">Post</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">Montørtimer per nytt besøk</t>
   </si>
   <si>
-    <t xml:space="preserve">Timepris, kr uten mva</t>
+    <t xml:space="preserve">Timepris, kr uten merverdiavgift</t>
   </si>
   <si>
     <t xml:space="preserve">Kanal fra Tom til montøren</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">Tom koder, SMS-en er mediet, montøren dekoder. Kan montøren spørre om noe kvelden før? Boka skiller mellom enveis og toveis, direkte og indirekte.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 16, avsnitt 16.2 (kommunikasjonsmodellen, direkte og indirekte, enveis og toveis), 16.3 (årsaker hos avsender og mottaker) og 16.4 (tiltak). Servicebesøkene: MA04 og faktaarket. Nordlys Elektro AS er en konstruert casebedrift.</t>
+    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 16, avsnitt 16.2 (kommunikasjonsmodellen, direkte og indirekte, enveis og toveis), 16.3 (årsaker hos avsender og mottaker) og 16.4 (tiltak). Servicebesøkene: Markedsføring kap. 4 og faktaarket. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
     <t xml:space="preserve">Regnearket er øvingsstøtte. Det kan ikke siteres eller vises til i besvarelser, prosjektoppgaver eller eksamen; der gjelder læreboka og oppgitte primærkilder.</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">Samarbeid når partene har noe å lære av hverandre. Konfrontasjon når saken er viktig og må avgjøres raskt. For e: hvilken sak har et «alltid» i seg?</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 16, avsnitt 16.5 (konfliktens intensitetsnivåer), 16.6 (fire konflikttyper) og 16.7 (fem konflikthåndteringsstrategier, figur 16.3). Sakene er fra v4, sammendraget og appen til kap. 16. Nordlys Elektro AS er en konstruert casebedrift.</t>
+    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 16, avsnitt 16.5 (konfliktens intensitetsnivåer), 16.6 (fire konflikttyper) og 16.7 (fem konflikthåndteringsstrategier, figur 16.3). Sakene er fra versjon 4, sammendraget og appen til kap. 16. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
     <t xml:space="preserve">B2 · Fjell Elektro: lønnskravet, makten og den andre montøren</t>
@@ -1202,7 +1202,7 @@
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
         <v>23</v>
       </c>

--- a/pensum/ol16/OL16_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol16/OL16_Klasseoppgaver_v5.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="163">
   <si>
-    <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 16: Grupper, kommunikasjon og konflikt (V5)</t>
+    <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 16: Grupper, kommunikasjon og konflikt (versjon 5)</t>
   </si>
   <si>
     <t xml:space="preserve">LØM · Fagskolen Oslo, Avdeling Elkraft · versjon 5, oktober 2026</t>

--- a/pensum/ol16/OL16_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol16/OL16_Klasseoppgaver_v5.xlsx
@@ -95,7 +95,7 @@
     <t xml:space="preserve">Kort oppsummert: Avsenderen koder et budskap som går via et medium til mottakeren, som dekoder det (16.2, figur 16.2). Budskapet må være presist, og budskap og medium må være tilpasset hverandre. Direkte kommunikasjon gir bedre muligheter til å utdype, oppklare tvetydigheter og rydde vekk misforståelser. Årsaker til brudd ligger hos avsenderen (egen fortolkning, vag og utydelig, vanskelig språk, dobbeltkommunikasjon) og hos mottakeren (selektiv, sympatier og antipatier, dårlig lytter) (16.3). Ledelsen har særlig ansvar for at relevant informasjon i tilstrekkelige mengder når dem som trenger den, når de trenger den (16.4).</t>
   </si>
   <si>
-    <t xml:space="preserve">Casen er lagt til 2026/2027. Servicemontørene i Nordlys kjører hjemmefra rett til første kunde. Kundene ringer Tom, og Tom sender oppdraget på SMS til montøren kvelden før, for eksempel «Jordfeil, Haugveien 12, kl. 8». I vårhalvåret hadde serviceavdelingen 105 besøk. 9 av dem måtte gjøres på nytt fordi det kunden hadde sagt til Tom, ikke nådde montøren: montøren hadde ikke med riktig del, kunden var ikke hjemme, eller sikringsskapet sto et annet sted enn montøren trodde. Hvert nytt besøk tok 3 montørtimer som ikke kunne faktureres. Timeprisen er 890 kr uten merverdiavgift. Tom sier: «De leser ikke meldingene ordentlig.» Gå fram slik: regn andelen og hva det kostet, finn leddet i kommunikasjonsmodellen som sviktet, sorter tiltakene, og vurder til slutt Toms forklaring.</t>
+    <t xml:space="preserve">Casen er lagt til 2026/2027. Servicemontørene i Nordlys kjører hjemmefra rett til første kunde. Kundene ringer Tom, og Tom sender oppdraget på SMS til montøren kvelden før, for eksempel «Jordfeil, Haugveien 12, kl. 8». I vårhalvåret hadde serviceavdelingen 105 besøk. 9 av dem måtte gjøres på nytt fordi det kunden hadde sagt til Tom, ikke nådde montøren: montøren hadde ikke med riktig del, kunden var ikke hjemme, eller sikringsskapet sto et annet sted enn montøren trodde. Hvert nytt besøk tok 3 montørtimer som ikke kunne faktureres. Timeprisen Nordlys tar av kunden, er 890 kr uten merverdiavgift (faktaarket). Tom sier: «De leser ikke meldingene ordentlig.» Gå fram slik: regn andelen og hva det kostet, finn leddet i kommunikasjonsmodellen som sviktet, sorter tiltakene, og vurder til slutt Toms forklaring.</t>
   </si>
   <si>
     <t xml:space="preserve">Post</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">Kort oppsummert: En gruppe er to eller flere personer som kommuniserer eller gjør noe sammen, og som selv oppfatter seg som en gruppe (16.1). Formelle grupper er målrettede, hvert medlem har en rolle, og det kreves formelle kvalifikasjoner; uformelle grupper bygger på felles interesser og trivsel. Når det verbale og det nonverbale budskapet ikke stemmer, er det stor sannsynlighet for at det nonverbale trenger gjennom, og avsenderen mister troverdighet (16.2). Boka anbefaler blant annet regelmessige, godt forberedte møter, utnyttelse av uformelle kanaler, aktiv lytting og medarbeidersamtaler (16.4).</t>
   </si>
   <si>
-    <t xml:space="preserve">Fjell Elektro AS har to montører og eieren Mona Fjell, som er daglig leder og faglig ansvarlig og jobber halve tiden ute på oppdrag. Jobbene fordeles over kaffen hver morgen, og hver mandag har de tre et møte på 30 minutter. Fjell har 46 arbeidsuker i året, og timeprisen er 890 kr. De to montørene spiller fotball sammen hver fredag. På mandagsmøtet sier Mona: «Si fra hvis noe er galt, døra mi er alltid åpen», mens hun leser på mobilen og reiser seg. Den ene montøren har sagt til den andre: «Mona spør aldri hvordan det går med oss.» Gå fram slik: sorter gruppene, gi det som skjer på møtet et navn, regn hva møtet koster i fakturerbar tid, og vurder til slutt hva Mona bør gjøre.</t>
+    <t xml:space="preserve">Fjell Elektro AS har to montører og eieren Mona Fjell, som er daglig leder og faglig ansvarlig og jobber halve tiden ute på oppdrag. Jobbene fordeles over kaffen hver morgen, og hver mandag har de tre et møte på 30 minutter. Fjell har 46 arbeidsuker i året, og timeprisen Fjell tar av kunden, er 890 kr (Fjells faktaark). De to montørene spiller fotball sammen hver fredag. På mandagsmøtet sier Mona: «Si fra hvis noe er galt, døra mi er alltid åpen», mens hun leser på mobilen og reiser seg. Den ene montøren har sagt til den andre: «Mona spør aldri hvordan det går med oss.» Gå fram slik: sorter gruppene, gi det som skjer på møtet et navn, regn hva møtet koster i fakturerbar tid, og vurder til slutt hva Mona bør gjøre.</t>
   </si>
   <si>
     <t xml:space="preserve">Forutsetning</t>
